--- a/data/trans_orig/P41C1_AOS_2023_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41C1_AOS_2023_R-Clase-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años que han tardado en que algún miembro de la pareja se quede embarazada</t>
+          <t>Tiempo medio en años que han tardado en que algún miembro de la pareja se quede embarazada (tasa de respuesta: 93,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,08</t>
+          <t>1,2; 4,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,74</t>
+          <t>1,4; 3,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,35</t>
+          <t>1,58; 3,41</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,0</t>
+          <t>1,0; 4,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,02</t>
+          <t>1,72; 5,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 10,43</t>
+          <t>0,6; 7,51</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,08</t>
+          <t>1,74; 4,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 12,12</t>
+          <t>2,03; 11,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,74</t>
+          <t>2,42; 6,49</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,36</t>
+          <t>1,91; 4,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 8,69</t>
+          <t>2,56; 8,82</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,76</t>
+          <t>2,08; 5,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,31</t>
+          <t>2,61; 5,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,36</t>
+          <t>2,56; 4,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41C1_AOS_2023_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41C1_AOS_2023_R-Clase-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,45</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>2,34</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,23</t>
+          <t>1,32; 4,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,72</t>
+          <t>1,39; 3,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,41</t>
+          <t>1,58; 3,44</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,28</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,15</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>3,19</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,15</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,66</t>
+          <t>1,0; 5,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,89</t>
+          <t>1,64; 5,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,99</t>
+          <t>2,02; 5,08</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>2,94</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,0</t>
+          <t>0,7; 4,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 7,51</t>
+          <t>0,64; 7,75</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>3,05</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>3,82</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,11</t>
+          <t>1,9; 4,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,61</t>
+          <t>2,07; 12,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,49</t>
+          <t>2,54; 6,61</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>2,52</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>4,09</t>
         </is>
       </c>
     </row>
@@ -776,19 +776,19 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,28</t>
+          <t>1,41; 3,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,82</t>
+          <t>2,17; 7,86</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,59</t>
+          <t>3,47</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>3,27</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,25</t>
+          <t>2,12; 4,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,12</t>
+          <t>2,52; 5,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,5</t>
+          <t>2,52; 4,48</t>
         </is>
       </c>
     </row>
